--- a/docs/Login-Instruktur-GG.xlsx
+++ b/docs/Login-Instruktur-GG.xlsx
@@ -559,7 +559,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -618,7 +617,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>afifahGG</t>
+          <t>afifah</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -658,7 +657,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>annaGGMK</t>
+          <t>annadesi</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -698,7 +697,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>asriGGMK</t>
+          <t>asrigelv</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -738,7 +737,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>devi_GG</t>
+          <t>deviocta</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -778,7 +777,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>fendy</t>
+          <t>fendyher</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -818,7 +817,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>lailyGGPIK</t>
+          <t>lailysor</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -858,7 +857,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>luciaGG</t>
+          <t>luciacha</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -898,7 +897,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>oliviaGGPIK</t>
+          <t>oliviana</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -938,7 +937,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>silvester</t>
+          <t>silvest</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -978,7 +977,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>violaGG</t>
+          <t>violand</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
